--- a/data/1_production_model/static_tables/manual_corrections.xlsx
+++ b/data/1_production_model/static_tables/manual_corrections.xlsx
@@ -1,46 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="S:\projects\eGrid\production_model\users\gofortht\data\1_production_model\static_tables\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7DE75F5-AD3E-4299-A41C-41B645F32D28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="4" xr2:uid="{FA61C6A3-A5F8-4301-A228-D222830EB6CC}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="0" activeTab="4"/>
   </bookViews>
   <sheets>
-    <sheet name="epa_clean" sheetId="5" r:id="rId1"/>
-    <sheet name="eia_clean" sheetId="6" r:id="rId2"/>
-    <sheet name="generator_file" sheetId="2" r:id="rId3"/>
-    <sheet name="unit_file" sheetId="1" r:id="rId4"/>
-    <sheet name="plant_file" sheetId="3" r:id="rId5"/>
+    <sheet name="epa_clean" sheetId="5" state="visible" r:id="rId1"/>
+    <sheet name="eia_clean" sheetId="6" state="visible" r:id="rId2"/>
+    <sheet name="generator_file" sheetId="2" state="visible" r:id="rId3"/>
+    <sheet name="unit_file" sheetId="1" state="visible" r:id="rId4"/>
+    <sheet name="plant_file" sheetId="3" state="visible" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="76">
   <si>
     <t>plant_id</t>
   </si>
@@ -256,13 +233,26 @@
   </si>
   <si>
     <t>72-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GT11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">add</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GT12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STG</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <numFmts count="0"/>
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -271,18 +261,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <b/>
     </font>
     <font>
-      <sz val="8"/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -308,8 +295,8 @@
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -646,16 +633,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D934C9D8-7DA6-4C13-BBA3-1B260AEBF0C8}">
-  <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="2" max="2" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.140625" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="17.85546875" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="7.28515625" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>59</v>
       </c>
@@ -669,25 +656,25 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>2024</v>
-      </c>
-      <c r="B2">
+    <row r="2">
+      <c r="A2" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B2" t="n">
         <v>880004</v>
       </c>
       <c r="C2" t="s">
         <v>0</v>
       </c>
-      <c r="D2">
+      <c r="D2" t="n">
         <v>57788</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3">
+    <row r="3">
+      <c r="A3" t="n">
         <v>2023</v>
       </c>
-      <c r="B3">
+      <c r="B3" t="n">
         <v>10154</v>
       </c>
       <c r="C3" t="s">
@@ -699,20 +686,21 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD042B8F-EA7C-4084-B7F4-709825082C60}">
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="2" max="2" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.140625" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="12.28515625" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="17.85546875" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>59</v>
       </c>
@@ -726,11 +714,11 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2">
+    <row r="2">
+      <c r="A2" t="n">
         <v>2024</v>
       </c>
-      <c r="B2">
+      <c r="B2" t="n">
         <v>60910</v>
       </c>
       <c r="C2" s="3" t="s">
@@ -740,24 +728,66 @@
         <v>40</v>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B3" t="n">
+        <v>66918</v>
+      </c>
+      <c r="C3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D3" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B4" t="n">
+        <v>66918</v>
+      </c>
+      <c r="C4" t="s">
+        <v>74</v>
+      </c>
+      <c r="D4" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B5" t="n">
+        <v>66918</v>
+      </c>
+      <c r="C5" t="s">
+        <v>75</v>
+      </c>
+      <c r="D5" t="s">
+        <v>73</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{791B152A-9A17-4C98-BF21-937C78FED9AB}">
-  <dimension ref="A1:F12"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="3" max="3" width="18.5703125" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.5703125" style="3" customWidth="1"/>
-    <col min="5" max="5" width="17.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.5703125" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.5703125" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="18.5703125" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="17.7109375" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="15.5703125" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>59</v>
       </c>
@@ -777,14 +807,14 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>2024</v>
-      </c>
-      <c r="B2">
+    <row r="2">
+      <c r="A2" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B2" t="n">
         <v>7512</v>
       </c>
-      <c r="C2" s="3">
+      <c r="C2" s="3" t="n">
         <v>1</v>
       </c>
       <c r="E2" t="s">
@@ -794,14 +824,14 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>2024</v>
-      </c>
-      <c r="B3">
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B3" t="n">
         <v>7512</v>
       </c>
-      <c r="C3" s="3">
+      <c r="C3" s="3" t="n">
         <v>2</v>
       </c>
       <c r="E3" t="s">
@@ -811,14 +841,14 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>2024</v>
-      </c>
-      <c r="B4">
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B4" t="n">
         <v>7512</v>
       </c>
-      <c r="C4" s="3">
+      <c r="C4" s="3" t="n">
         <v>3</v>
       </c>
       <c r="E4" t="s">
@@ -828,11 +858,11 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <v>2024</v>
-      </c>
-      <c r="B5">
+    <row r="5">
+      <c r="A5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B5" t="n">
         <v>664</v>
       </c>
       <c r="C5" s="3" t="s">
@@ -845,22 +875,22 @@
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6">
-        <v>2024</v>
-      </c>
-      <c r="B6">
+    <row r="6">
+      <c r="A6" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B6" t="n">
         <v>56032</v>
       </c>
       <c r="E6" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7">
+    <row r="7">
+      <c r="A7" t="n">
         <v>2023</v>
       </c>
-      <c r="B7">
+      <c r="B7" t="n">
         <v>55350</v>
       </c>
       <c r="C7" s="3" t="s">
@@ -876,11 +906,11 @@
         <v>35</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8">
+    <row r="8">
+      <c r="A8" t="n">
         <v>2023</v>
       </c>
-      <c r="B8">
+      <c r="B8" t="n">
         <v>55350</v>
       </c>
       <c r="C8" s="3" t="s">
@@ -896,33 +926,35 @@
         <v>34</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11">
       <c r="C11"/>
       <c r="D11"/>
       <c r="F11"/>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12">
       <c r="C12"/>
       <c r="D12"/>
       <c r="F12"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C1A8242-D17A-4DAB-8319-EC8C1026D049}">
-  <dimension ref="A1:F33"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="2" max="3" width="8.140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="30.85546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.140625" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="8.140625" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="12.85546875" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="20.28515625" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="30.85546875" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>59</v>
       </c>
@@ -942,25 +974,25 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>2024</v>
-      </c>
-      <c r="B2" s="3">
+    <row r="2">
+      <c r="A2" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B2" s="3" t="n">
         <v>55248</v>
       </c>
       <c r="E2" t="s">
         <v>0</v>
       </c>
-      <c r="F2" s="3">
+      <c r="F2" s="3" t="n">
         <v>2847</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>2024</v>
-      </c>
-      <c r="B3" s="3">
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B3" s="3" t="n">
         <v>2847</v>
       </c>
       <c r="E3" t="s">
@@ -970,14 +1002,14 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>2024</v>
-      </c>
-      <c r="B4" s="3">
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B4" s="3" t="n">
         <v>2707</v>
       </c>
-      <c r="C4" s="3">
+      <c r="C4" s="3" t="n">
         <v>1</v>
       </c>
       <c r="E4" t="s">
@@ -987,14 +1019,14 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <v>2024</v>
-      </c>
-      <c r="B5" s="3">
+    <row r="5">
+      <c r="A5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B5" s="3" t="n">
         <v>2707</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C5" s="3" t="n">
         <v>2</v>
       </c>
       <c r="E5" t="s">
@@ -1004,14 +1036,14 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6">
-        <v>2024</v>
-      </c>
-      <c r="B6" s="3">
+    <row r="6">
+      <c r="A6" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B6" s="3" t="n">
         <v>2707</v>
       </c>
-      <c r="C6" s="3">
+      <c r="C6" s="3" t="n">
         <v>3</v>
       </c>
       <c r="E6" t="s">
@@ -1021,14 +1053,14 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7">
-        <v>2024</v>
-      </c>
-      <c r="B7" s="3">
+    <row r="7">
+      <c r="A7" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B7" s="3" t="n">
         <v>2707</v>
       </c>
-      <c r="C7" s="3">
+      <c r="C7" s="3" t="n">
         <v>4</v>
       </c>
       <c r="E7" t="s">
@@ -1038,19 +1070,19 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8">
+    <row r="8">
+      <c r="A8" t="n">
         <v>2023</v>
       </c>
-      <c r="B8" s="3">
+      <c r="B8" s="3" t="n">
         <v>7832</v>
       </c>
       <c r="E8" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9">
+    <row r="9">
+      <c r="A9" t="n">
         <v>2023</v>
       </c>
       <c r="B9" s="3" t="s">
@@ -1060,8 +1092,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10">
+    <row r="10">
+      <c r="A10" t="n">
         <v>2023</v>
       </c>
       <c r="B10" s="3" t="s">
@@ -1071,11 +1103,11 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11">
-        <v>2024</v>
-      </c>
-      <c r="B11" s="3">
+    <row r="11">
+      <c r="A11" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B11" s="3" t="n">
         <v>7063</v>
       </c>
       <c r="C11" s="3" t="s">
@@ -1091,9 +1123,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12">
-        <v>2024</v>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>2025</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>25</v>
@@ -1108,9 +1140,9 @@
         <v>30</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13">
-        <v>2024</v>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>2025</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>25</v>
@@ -1125,9 +1157,9 @@
         <v>30</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14">
-        <v>2024</v>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>2025</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>25</v>
@@ -1142,9 +1174,9 @@
         <v>30</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15">
-        <v>2024</v>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>2025</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>25</v>
@@ -1159,9 +1191,9 @@
         <v>30</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16">
-        <v>2024</v>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>2025</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>25</v>
@@ -1176,9 +1208,9 @@
         <v>32</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17">
-        <v>2024</v>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>2025</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>25</v>
@@ -1193,9 +1225,9 @@
         <v>32</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18">
-        <v>2024</v>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>2025</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>41</v>
@@ -1213,9 +1245,9 @@
         <v>13</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19">
-        <v>2024</v>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>2025</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>46</v>
@@ -1233,9 +1265,9 @@
         <v>51</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20">
-        <v>2024</v>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>2025</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>46</v>
@@ -1253,9 +1285,9 @@
         <v>51</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21">
-        <v>2024</v>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>2025</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>46</v>
@@ -1273,9 +1305,9 @@
         <v>51</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22">
-        <v>2024</v>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>2025</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>46</v>
@@ -1293,9 +1325,9 @@
         <v>51</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23">
-        <v>2024</v>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>2025</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>46</v>
@@ -1313,9 +1345,9 @@
         <v>30</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24">
-        <v>2024</v>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2025</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>46</v>
@@ -1333,8 +1365,8 @@
         <v>30</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25">
+    <row r="25">
+      <c r="A25" t="n">
         <v>2024</v>
       </c>
       <c r="B25" s="3" t="s">
@@ -1347,8 +1379,8 @@
         <v>55</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26">
+    <row r="26">
+      <c r="A26" t="n">
         <v>2024</v>
       </c>
       <c r="B26" s="3" t="s">
@@ -1361,9 +1393,9 @@
         <v>58</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27">
-        <v>2024</v>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>2025</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>61</v>
@@ -1381,9 +1413,9 @@
         <v>68</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28">
-        <v>2024</v>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>2025</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>61</v>
@@ -1401,9 +1433,9 @@
         <v>68</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29">
-        <v>2024</v>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>2025</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>61</v>
@@ -1421,9 +1453,9 @@
         <v>68</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30">
-        <v>2024</v>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>2025</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>61</v>
@@ -1441,9 +1473,9 @@
         <v>68</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31">
-        <v>2024</v>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>2025</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>61</v>
@@ -1461,9 +1493,9 @@
         <v>68</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32">
-        <v>2024</v>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>2025</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>69</v>
@@ -1481,9 +1513,9 @@
         <v>68</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33">
-        <v>2024</v>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>2025</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>69</v>
@@ -1502,22 +1534,21 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A26772A-0AAB-4516-99B5-5272EE829F50}">
-  <dimension ref="A1:E11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="2" max="2" width="8.7109375" style="3"/>
-    <col min="3" max="3" width="19.5703125" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.5703125" customWidth="1"/>
+    <col min="3" max="3" width="19.5703125" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="11.5703125" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>59</v>
       </c>
@@ -1531,73 +1562,91 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B2" s="3">
+    <row r="2">
+      <c r="A2" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B2" s="3" t="n">
         <v>54975</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D2">
+      <c r="D2" t="n">
         <v>32.380032</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B3" s="3">
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B3" s="3" t="n">
         <v>62262</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D3">
+      <c r="D3" t="n">
         <v>42.899028999999999</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B4" s="3">
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B4" s="3" t="n">
         <v>54975</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D4">
+      <c r="D4" t="n">
         <v>-106.753716</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B5" s="3">
+    <row r="5">
+      <c r="A5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B5" s="3" t="n">
         <v>62262</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D5">
+      <c r="D5" t="n">
         <v>-75.458455999999998</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6">
+      <c r="A6" t="n">
+        <v>2025</v>
+      </c>
       <c r="B6" s="3" t="s">
         <v>45</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D6">
+      <c r="D6" t="n">
         <v>42.502749999999999</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7">
+      <c r="A7" t="n">
+        <v>2025</v>
+      </c>
       <c r="B7" s="3" t="s">
         <v>45</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D7">
+      <c r="D7" t="n">
         <v>-79.281723</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11">
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
       <c r="D11" s="4"/>
@@ -1605,5 +1654,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>